--- a/output/pdf_financials_xlsx/BBM.xlsx
+++ b/output/pdf_financials_xlsx/BBM.xlsx
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.8181580000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.066081</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.026393</v>
       </c>
     </row>
     <row r="35">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.8181580000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.066081</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.026393</v>
       </c>
     </row>
     <row r="37">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.338284</v>
+        <v>0.520126</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.078254</v>
+        <v>0.012173</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.035505</v>
+        <v>0.009112</v>
       </c>
     </row>
     <row r="49">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048787</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001947</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001903</v>
       </c>
     </row>
     <row r="125">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048787</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001947</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001903</v>
       </c>
     </row>
     <row r="126">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4846,7 +4846,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>-0.048787</v>
       </c>
@@ -5805,14 +5809,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-1.724378</v>
+        <v>1.724378</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-1.077638</v>
+        <v>1.077638</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BBM.xlsx
+++ b/output/pdf_financials_xlsx/BBM.xlsx
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.024494</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.009003000000000001</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -4788,7 +4788,11 @@
           <t>Proceeds from disposal of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.024494</v>
       </c>

--- a/output/pdf_financials_xlsx/BBM.xlsx
+++ b/output/pdf_financials_xlsx/BBM.xlsx
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.010481</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.002362</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.001928</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.310364</v>
+        <v>0.320845</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.391439</v>
+        <v>0.393801</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.280089</v>
+        <v>0.282017</v>
       </c>
     </row>
     <row r="42">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.520126</v>
+        <v>0.509645</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.012173</v>
+        <v>0.009811</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.009112</v>
+        <v>0.007184</v>
       </c>
     </row>
     <row r="49">
@@ -4821,7 +4821,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.382917</v>
       </c>
